--- a/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>MESA</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E8" s="3">
         <v>114700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>121800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>147200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>125600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>134400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>123200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>147800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>130800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>125200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>97300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>150400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>108000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>73100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>179900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>184000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>187800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>180200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>177100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>178200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>177500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>171700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>167600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>164700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>157300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>167000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>159100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>160200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>160500</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E9" s="3">
         <v>103500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>101700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>110700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>98300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>102200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>99200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>118100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>117500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>103900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>100100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>101200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>91300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>68500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>131000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>123300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>124500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>121400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>110000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>108200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>108000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>119100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>142300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>21200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E10" s="3">
         <v>11200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>27300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>29700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-2800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>49200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>48900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>60700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>63300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>58800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>67100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>70000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>69500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>52600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>154000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>146900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>158600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>137900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>136300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>135300</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,79 +1279,82 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E14" s="3">
         <v>30500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>16700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>133000</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>39500</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
-        <v>-26100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>-26100</v>
       </c>
       <c r="M14" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="N14" s="3">
         <v>-51500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-12300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-40800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-43000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>9500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>15100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1342,8 +1362,8 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1351,83 +1371,86 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E15" s="3">
         <v>15300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>15200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>20100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>20900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20500</v>
-      </c>
-      <c r="O15" s="3">
-        <v>20600</v>
       </c>
       <c r="P15" s="3">
         <v>20600</v>
       </c>
       <c r="Q15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="R15" s="3">
         <v>20500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>20600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>20500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>19800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>19300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>18500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>17400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>16000</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="3">
         <v>15900</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E17" s="3">
         <v>154900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>148700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>144700</v>
       </c>
-      <c r="G17" s="3">
-        <v>267200</v>
-      </c>
       <c r="H17" s="3">
+        <v>262500</v>
+      </c>
+      <c r="I17" s="3">
         <v>134200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>168000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>151700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>125700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>110800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>80500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>122400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>84200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>57900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>166000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>156800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>157400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>163100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>146400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>138900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>135700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>172200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>151300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>149700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>134600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>130600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>138700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>139400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-40200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-141600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-136900</v>
+      </c>
+      <c r="I18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-44800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>23800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>30400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>30700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>39300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>41800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>15000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>22700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>36400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,261 +1714,268 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
-        <v>3500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6700</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-12500</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-11900</v>
       </c>
       <c r="AC20" s="3">
         <v>-11900</v>
       </c>
       <c r="AD20" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-23000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-118500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>35400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>37000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>48500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>44600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>35900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>35300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>47500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>51100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>37100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>50400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>58400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>59300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>15500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>18600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>30900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>26000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>40100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E22" s="3">
         <v>12000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14100</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>14100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-50300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-37200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-148600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-55200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>17100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>25000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>26600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-33000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-12400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-47600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-115600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-42800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>12200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>13200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-47600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-115600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-42800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>13200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2526,8 +2587,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2544,21 +2605,21 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>600</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>21400</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I32" s="3">
         <v>4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6700</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>13300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>12500</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>11900</v>
       </c>
       <c r="AC32" s="3">
         <v>11900</v>
       </c>
       <c r="AD32" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AE32" s="3">
         <v>10200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-47600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-115600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-42800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>12200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>13200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>22600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>15400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-47600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-115600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-42800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>12200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>13200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>22600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>15400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,80 +3351,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E41" s="3">
         <v>48300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>51400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>56100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>57700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>54400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>75900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>102300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>120500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>180400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>147900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>181300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>99400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>64900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>57800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>68900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>79900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>77700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>88600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>103300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>41700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>52700</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3414,14 +3504,14 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>15000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>19900</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3434,8 +3524,8 @@
       <c r="AB42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3443,80 +3533,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>23100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>21600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>17000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3532,49 +3625,52 @@
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E44" s="3">
         <v>28700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26700</v>
-      </c>
-      <c r="H44" s="3">
-        <v>26300</v>
       </c>
       <c r="I44" s="3">
         <v>26300</v>
       </c>
       <c r="J44" s="3">
+        <v>26300</v>
+      </c>
+      <c r="K44" s="3">
         <v>25200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>24500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>24700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>23000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23000</v>
-      </c>
-      <c r="P44" s="3">
-        <v>22400</v>
       </c>
       <c r="Q44" s="3">
         <v>22400</v>
@@ -3583,29 +3679,29 @@
         <v>22400</v>
       </c>
       <c r="S44" s="3">
+        <v>22400</v>
+      </c>
+      <c r="T44" s="3">
         <v>21300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>20300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>17400</v>
-      </c>
-      <c r="W44" s="3">
-        <v>15700</v>
       </c>
       <c r="X44" s="3">
         <v>15700</v>
       </c>
       <c r="Y44" s="3">
+        <v>15700</v>
+      </c>
+      <c r="Z44" s="3">
         <v>15400</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3621,80 +3717,83 @@
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E45" s="3">
         <v>100500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>12300</v>
       </c>
       <c r="M45" s="3">
         <v>12300</v>
       </c>
       <c r="N45" s="3">
+        <v>12300</v>
+      </c>
+      <c r="O45" s="3">
         <v>16500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>44600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>50100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>51100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>46700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>43300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>51000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3710,80 +3809,83 @@
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>138600</v>
+      </c>
+      <c r="E46" s="3">
         <v>181100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>117100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>102000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>98300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>95400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>120000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>138300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>158400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>222400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>197100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>236000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>155600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>112600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>98300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>112200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>157800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>158200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>160100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>173700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>197900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>122400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>136200</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3799,35 +3901,38 @@
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E47" s="3">
         <v>18200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>15200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3849,30 +3954,30 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3">
         <v>3900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3">
         <v>2500</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3888,80 +3993,83 @@
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>707700</v>
+      </c>
+      <c r="E48" s="3">
         <v>721100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>879600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>957400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>908300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1138700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1144100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1246400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1245000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1262100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1286200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1308700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1335700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1365200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1383600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1407300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1273600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1286000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1237600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1247800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1250800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1239500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1182800</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3977,8 +4085,11 @@
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3992,65 +4103,65 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>3800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11500</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,80 +4361,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E52" s="3">
         <v>41600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>43300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>86700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>89900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>46400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>33500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9600</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,80 +4545,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>898500</v>
+      </c>
+      <c r="E54" s="3">
         <v>962000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1055400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1159500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1115600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1320200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1353400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1434500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1456600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1525000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1519600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1554800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1501900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1495300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1511700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1542000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1451900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1466000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1425300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1444000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1472400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1389600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1342600</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,80 +4707,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E57" s="3">
         <v>51900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>66800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>76700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>61500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>52800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>70000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>47600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>53200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>39900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>49200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>47800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>49900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>33600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>40500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>54300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>44700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>41900</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4666,80 +4797,83 @@
       <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E58" s="3">
         <v>124300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>145000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>88800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>97200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>112800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>111700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>111100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>111700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>107700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>104000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>99700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>189300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>176900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>168200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>166100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>165900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>163600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>147100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>149800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>155200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>149900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>144500</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4755,80 +4889,83 @@
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E59" s="3">
         <v>45900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>57900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>60700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>76400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>85000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>115400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>87400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>140600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>110800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>91200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>83200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>82100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>40900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>39000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>40900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>41900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>52300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>33900</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4844,80 +4981,83 @@
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>267900</v>
+      </c>
+      <c r="E60" s="3">
         <v>222100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>242100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>186300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>214500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>240300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>249400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>250400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>258200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>276000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>261400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>287900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>353300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>308000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>300600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>295900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>256700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>245900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>226700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>231200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>251400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>246900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>220400</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4933,80 +5073,83 @@
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>364700</v>
+      </c>
+      <c r="E61" s="3">
         <v>441900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>463600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>597800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>502500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>523200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>521500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>547400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>539700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>585800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>600100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>624100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>542500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>586900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>619800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>641000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>677400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>717500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>696900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>727800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>760200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>828500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>784500</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5022,80 +5165,83 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E62" s="3">
         <v>70000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>74400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>75700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>90400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>133600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>150000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>162200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>170700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>168600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>167300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>158500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>148300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>154900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>150000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>166900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>91900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>89900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>92500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>89700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>86400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>81600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>89100</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,80 +5533,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>698400</v>
+      </c>
+      <c r="E66" s="3">
         <v>734100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>780100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>859700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>807400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>897100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>920800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>960000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>968600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1030300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1028700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1070500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1044100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1049800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1070400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1103800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1026000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1053200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1016000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1048800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1097900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1157000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1093900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,80 +6027,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-42800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>39900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>49000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>164600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>174600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>217400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>231700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>239200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>234900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>229200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>215100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>203700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>200300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>198400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>187400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>175100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>172100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>158900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>139800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>119900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>133400</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,80 +6395,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E76" s="3">
         <v>227900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>275200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>299800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>308200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>423000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>432500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>474500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>488000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>494700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>490800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>484300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>457900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>445500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>441400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>438200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>425900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>412700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>409300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>395200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>374500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>232600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>248700</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-47600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-115600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-42800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>12200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>13200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>22600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>15400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,97 +6804,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E83" s="3">
         <v>15300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>20100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>20600</v>
       </c>
       <c r="P83" s="3">
         <v>20600</v>
       </c>
       <c r="Q83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="R83" s="3">
         <v>20500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>20600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>19800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>19300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>18500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>16000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15600</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>52600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>79300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>71100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>38400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>27000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>38200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>37600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>44300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>25600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>44100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>55800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>22000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>13100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>28100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>36000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>22200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,97 +7482,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-82500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-81500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E94" s="3">
         <v>47200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>78400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>41700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-77500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-20300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-37400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-84200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-45100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-80700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-38300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-28600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-45100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-23100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-35000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-20400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-36700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-39800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>35400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-38300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-38700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>43200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>51300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-32700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>14300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-22900</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-26400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-59900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>32500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>82100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-14900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>61600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-26300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>33900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>MESA</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>118800</v>
+      </c>
+      <c r="E8" s="3">
         <v>114400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>114700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>121800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>147200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>125600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>134400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>123200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>147800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>130800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>125200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>97300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>150400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>108000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>73100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>179900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>184000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>187800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>180200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>177100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>178200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>177500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>171700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>167600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>164700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>157300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>167000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>159100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>160200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>160500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E9" s="3">
         <v>106800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>103500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>101700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>110700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>98300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>102200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>99200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>118100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>117500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>103900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>100100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>101200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>91300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>68500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>131000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>123300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>124500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>121400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>110000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>108200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>108000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>119100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>142300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>21200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E10" s="3">
         <v>7600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>36500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>27300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>32200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>21300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-2800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>49200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>48900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>60700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>63300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>58800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>67100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>70000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>69500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>52600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>154000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>146900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>158600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>137900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>136300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>135300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,82 +1298,85 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E14" s="3">
         <v>3400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>30500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>133000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>39500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
-        <v>-26100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>-26100</v>
       </c>
       <c r="N14" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="O14" s="3">
         <v>-51500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-12300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-43000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>9500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>15100</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1365,8 +1384,8 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1383,77 +1405,77 @@
         <v>13300</v>
       </c>
       <c r="E15" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F15" s="3">
         <v>15300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>15200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>20700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>20500</v>
-      </c>
-      <c r="P15" s="3">
-        <v>20600</v>
       </c>
       <c r="Q15" s="3">
         <v>20600</v>
       </c>
       <c r="R15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="S15" s="3">
         <v>20500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>20600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>20500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>19800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>19300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>18500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>17400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>16000</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB15" s="3">
         <v>15900</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>167200</v>
+      </c>
+      <c r="E17" s="3">
         <v>134600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>154900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>148700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>144700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>262500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>134200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>168000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>151700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>125700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>110800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>80500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>122400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>84200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>57900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>166000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>156800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>157400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>163100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>146400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>138900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>135700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>172200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>151300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>149700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>134600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>130600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>138700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>139400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-48400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-40200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-26900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-136900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-44800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>27200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>30400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>30700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>39300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>41800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>15000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>22700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>36400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>20800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,270 +1747,277 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1200</v>
       </c>
       <c r="H20" s="3">
         <v>-1200</v>
       </c>
       <c r="I20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6700</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-12500</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-11900</v>
       </c>
       <c r="AD20" s="3">
         <v>-11900</v>
       </c>
       <c r="AE20" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-23000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-118500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>16300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>35400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>48500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>44600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>35900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>35300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>47500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>51100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>37100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>50400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>58400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>59300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>15500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>18600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>30900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>26000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>40100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E22" s="3">
         <v>13600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3">
         <v>14100</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1991,192 +2030,201 @@
       <c r="AF22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-31300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-50300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-37200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-148600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-55200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>17100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>17300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>25000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>26600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>24500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-33000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-12400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-47600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-35100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-115600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-42800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>13200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-47600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-115600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-42800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>13200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>15400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>6600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2590,8 +2650,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2608,21 +2668,21 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>600</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>21400</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1200</v>
       </c>
       <c r="H32" s="3">
         <v>1200</v>
       </c>
       <c r="I32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="3">
         <v>4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6700</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>13300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>12500</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>11900</v>
       </c>
       <c r="AD32" s="3">
         <v>11900</v>
       </c>
       <c r="AE32" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AF32" s="3">
         <v>10200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-47600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-115600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-42800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>13200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>15400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>6600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-47600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-115600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-42800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>13200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>15400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>6600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,83 +3437,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E41" s="3">
         <v>32900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>48300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>56100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>57700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>54400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>75900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>102300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>120500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>180400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>147900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>181300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>99400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>64900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>57800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>68900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>79900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>77700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>88600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>103300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>41700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>52700</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3444,8 +3530,11 @@
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3507,14 +3596,14 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>15000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>19900</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3527,8 +3616,8 @@
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3536,83 +3625,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E43" s="3">
         <v>8300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>21600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>17000</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3628,52 +3720,55 @@
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E44" s="3">
         <v>29200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>28700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>25500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26700</v>
-      </c>
-      <c r="I44" s="3">
-        <v>26300</v>
       </c>
       <c r="J44" s="3">
         <v>26300</v>
       </c>
       <c r="K44" s="3">
+        <v>26300</v>
+      </c>
+      <c r="L44" s="3">
         <v>25200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>24500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>23000</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>22400</v>
       </c>
       <c r="R44" s="3">
         <v>22400</v>
@@ -3682,29 +3777,29 @@
         <v>22400</v>
       </c>
       <c r="T44" s="3">
+        <v>22400</v>
+      </c>
+      <c r="U44" s="3">
         <v>21300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>20300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>19200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>17400</v>
-      </c>
-      <c r="X44" s="3">
-        <v>15700</v>
       </c>
       <c r="Y44" s="3">
         <v>15700</v>
       </c>
       <c r="Z44" s="3">
+        <v>15700</v>
+      </c>
+      <c r="AA44" s="3">
         <v>15400</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3720,83 +3815,86 @@
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>99900</v>
+      </c>
+      <c r="E45" s="3">
         <v>68100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>12300</v>
       </c>
       <c r="N45" s="3">
         <v>12300</v>
       </c>
       <c r="O45" s="3">
+        <v>12300</v>
+      </c>
+      <c r="P45" s="3">
         <v>16500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>44600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>50100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>46700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>44700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>43300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>51000</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3812,83 +3910,86 @@
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>150300</v>
+      </c>
+      <c r="E46" s="3">
         <v>138600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>181100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>117100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>102000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>98300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>95400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>120000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>138300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>158400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>222400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>197100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>236000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>155600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>112600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>98300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>112200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>157800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>158200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>160100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>173700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>197900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>122400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>136200</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3904,38 +4005,41 @@
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E47" s="3">
         <v>20300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>15200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>19000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3957,30 +4061,30 @@
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U47" s="3">
         <v>3900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA47" s="3">
         <v>2500</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3996,83 +4100,86 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>543400</v>
+      </c>
+      <c r="E48" s="3">
         <v>707700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>721100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>879600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>957400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>908300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1138700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1144100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1246400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1245000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1262100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1286200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1308700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1335700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1365200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1383600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1407300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1273600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1286000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1237600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1247800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1250800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1239500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1182800</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4088,13 +4195,16 @@
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4106,65 +4216,65 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>3800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11500</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,83 +4480,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E52" s="3">
         <v>31800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>41600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>86700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>89900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>63400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>63200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>46400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>33500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9600</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,83 +4670,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>775600</v>
+      </c>
+      <c r="E54" s="3">
         <v>898500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>962000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1055400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1159500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1115600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1320200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1353400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1434500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1456600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1525000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1519600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1554800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1501900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1495300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1511700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1542000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1451900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1466000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1425300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1444000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1472400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1389600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1342600</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4640,8 +4765,11 @@
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,83 +4837,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E57" s="3">
         <v>59000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>51900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>48500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>51300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>59400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>66800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>76700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>61500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>52800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>70000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>53200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>39900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>49200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>47800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>49900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>33600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>54300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>44700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>41900</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4800,83 +4930,86 @@
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>156800</v>
+      </c>
+      <c r="E58" s="3">
         <v>163600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>124300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>145000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>88800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>97200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>112800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>111700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>111100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>111700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>107700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>104000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>99700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>189300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>176900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>168200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>166100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>165900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>163600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>147100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>149800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>155200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>149900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>144500</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4892,83 +5025,86 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E59" s="3">
         <v>45400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>45900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>48600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>46200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>57900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>60700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>61000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>76400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>85000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>115400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>87400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>140600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>110800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>91200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>83200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>82100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>40900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>39000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>40900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>41900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>52300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>33900</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4984,83 +5120,86 @@
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E60" s="3">
         <v>267900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>222100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>242100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>186300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>214500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>240300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>249400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>250400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>258200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>276000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>261400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>287900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>353300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>308000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>300600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>295900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>256700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>245900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>226700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>231200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>251400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>246900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>220400</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5076,83 +5215,86 @@
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>315500</v>
+      </c>
+      <c r="E61" s="3">
         <v>364700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>441900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>463600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>597800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>502500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>523200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>521500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>547400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>539700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>585800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>600100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>624100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>542500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>586900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>619800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>641000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>677400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>717500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>696900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>727800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>760200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>828500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>784500</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5168,83 +5310,86 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E62" s="3">
         <v>65800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>70000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>74400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>75700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>90400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>133600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>150000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>162200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>170700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>168600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>167300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>158500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>148300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>154900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>150000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>166900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>91900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>89900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>92500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>89700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>86400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>81600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>89100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,83 +5690,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>633000</v>
+      </c>
+      <c r="E66" s="3">
         <v>698400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>734100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>780100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>859700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>807400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>897100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>920800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>960000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>968600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1030300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1028700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1070500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1044100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1049800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1070400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1103800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1026000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1053200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1016000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1048800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1097900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1157000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1093900</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5628,8 +5785,11 @@
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,83 +6200,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-71100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-42800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>39900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>49000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>164600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>174600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>217400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>231700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>239200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>234900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>229200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>215100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>203700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>200300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>198400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>187400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>175100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>172100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>158900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>139800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>119900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>133400</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6122,8 +6295,11 @@
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,83 +6580,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E76" s="3">
         <v>200000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>227900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>275200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>299800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>308200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>423000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>432500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>474500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>488000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>494700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>490800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>484300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>457900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>445500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>441400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>438200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>425900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>412700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>409300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>395200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>374500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>232600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>248700</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6490,8 +6675,11 @@
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-57900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-47600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-115600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-42800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>13200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>15400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>6600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6814,91 +7012,94 @@
         <v>13300</v>
       </c>
       <c r="E83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F83" s="3">
         <v>15300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>19600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>20600</v>
       </c>
       <c r="Q83" s="3">
         <v>20600</v>
       </c>
       <c r="R83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="S83" s="3">
         <v>20500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>20500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>19800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>19300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>18500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>16000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15600</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>52600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>79300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>71100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>38400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>27000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>38200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>37600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>44300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>25600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>44100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>55800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>22000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>28100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>36000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>22200</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-82500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-81500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E94" s="3">
         <v>33300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>47200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>78400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>41700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-77500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8495,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-45100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-80700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-38300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-45100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-23100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-25500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-20400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-39800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>35400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-38300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-38700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>43200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>51300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-32700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>14300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-22900</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-26400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>32500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-33700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>82100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>34500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-14900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>61600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>22500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>33900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>MESA</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>131600</v>
+      </c>
+      <c r="E8" s="3">
         <v>118800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>114400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>114700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>121800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>147200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>125600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>134400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>123200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>147800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>130800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>125200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>97300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>150400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>108000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>73100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>179900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>184000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>187800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>180200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>177100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>178200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>177500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>171700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>167600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>164700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>157300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>167000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>159100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>160200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>160500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E9" s="3">
         <v>101600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>106800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>103500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>101700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>110700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>98300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>102200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>99200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>118100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>117500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>103900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>100100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>101200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>91300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>68500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>131000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>123300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>124500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>121400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>110000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>108200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>108000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>119100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>142300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>10400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>21200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E10" s="3">
         <v>17200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>36500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>27300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>32200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>29700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-2800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>49200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>48900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>60700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>63300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>58800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>67100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>70000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>69500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>52600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>154000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>22400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>146900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>158600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>137900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>136300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>135300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,85 +1318,88 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E14" s="3">
         <v>37400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>30500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>133000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>39500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
-        <v>-26100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>-26100</v>
       </c>
       <c r="O14" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="P14" s="3">
         <v>-51500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-40800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-43000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>9500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>15100</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1387,8 +1407,8 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1396,89 +1416,92 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>13300</v>
+        <v>9800</v>
       </c>
       <c r="E15" s="3">
         <v>13300</v>
       </c>
       <c r="F15" s="3">
+        <v>13300</v>
+      </c>
+      <c r="G15" s="3">
         <v>15300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>15200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>20700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>20600</v>
       </c>
       <c r="R15" s="3">
         <v>20600</v>
       </c>
       <c r="S15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="T15" s="3">
         <v>20500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>20600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>20500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>19800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>19300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>18500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>17400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>16000</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="3">
         <v>15900</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E17" s="3">
         <v>167200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>134600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>154900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>148700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>144700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>262500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>134200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>168000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>151700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>125700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>110800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>80500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>122400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>84200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>57900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>166000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>156800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>157400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>163100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>146400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>138900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>135700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>172200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>151300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>149700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>134600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>130600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>138700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>139400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-48400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-40200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-26900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-136900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-44800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>28000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>27200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>30400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>30700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>39300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>41800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>15000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>22700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>36400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>20400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,279 +1781,286 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-1200</v>
       </c>
       <c r="I20" s="3">
         <v>-1200</v>
       </c>
       <c r="J20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6700</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-12500</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-11900</v>
       </c>
       <c r="AE20" s="3">
         <v>-11900</v>
       </c>
       <c r="AF20" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-118500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>16300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>35400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>48500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>44600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>35900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>35300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>47500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>51100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>37100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>50400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>58400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>59300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>15500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>18600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>30900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>26000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>40100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E22" s="3">
         <v>11200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>10400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>14100</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2033,198 +2073,207 @@
       <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-57000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-50300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-37200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-148600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-55200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>17300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>25000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>24500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-33000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-12400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-57900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-47600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-115600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-42800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>13200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-57900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-47600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-115600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-42800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>13200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>15400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2653,8 +2714,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2671,21 +2732,21 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>600</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>21400</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1200</v>
       </c>
       <c r="I32" s="3">
         <v>1200</v>
       </c>
       <c r="J32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6700</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>13300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>12500</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>11900</v>
       </c>
       <c r="AE32" s="3">
         <v>11900</v>
       </c>
       <c r="AF32" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AG32" s="3">
         <v>10200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-57900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-47600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-115600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-42800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>13200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>22600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>15400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-57900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-47600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-115600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-42800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>13200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>22600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>15400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,86 +3524,87 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E41" s="3">
         <v>16100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>48300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>51400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>56100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>57700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>54400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>75900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>102300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>120500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>180400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>147900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>181300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>99400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>64900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>57800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>68900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>79900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>77700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>88600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>103300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>41700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>52700</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3533,8 +3620,11 @@
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3599,14 +3689,14 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>15000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>19900</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3619,8 +3709,8 @@
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -3628,86 +3718,89 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E43" s="3">
         <v>5500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>23100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>21600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>17000</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3723,55 +3816,58 @@
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E44" s="3">
         <v>28800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>29200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>28700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>26800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>25500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>26700</v>
-      </c>
-      <c r="J44" s="3">
-        <v>26300</v>
       </c>
       <c r="K44" s="3">
         <v>26300</v>
       </c>
       <c r="L44" s="3">
+        <v>26300</v>
+      </c>
+      <c r="M44" s="3">
         <v>25200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>24500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>23000</v>
-      </c>
-      <c r="R44" s="3">
-        <v>22400</v>
       </c>
       <c r="S44" s="3">
         <v>22400</v>
@@ -3780,29 +3876,29 @@
         <v>22400</v>
       </c>
       <c r="U44" s="3">
+        <v>22400</v>
+      </c>
+      <c r="V44" s="3">
         <v>21300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>20300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>19200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>17400</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>15700</v>
       </c>
       <c r="Z44" s="3">
         <v>15700</v>
       </c>
       <c r="AA44" s="3">
+        <v>15700</v>
+      </c>
+      <c r="AB44" s="3">
         <v>15400</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3818,86 +3914,89 @@
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E45" s="3">
         <v>99900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>68100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>12300</v>
       </c>
       <c r="O45" s="3">
         <v>12300</v>
       </c>
       <c r="P45" s="3">
+        <v>12300</v>
+      </c>
+      <c r="Q45" s="3">
         <v>16500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>44600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>50100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>51100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>46700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>44700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>43300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>51000</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3913,86 +4012,89 @@
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E46" s="3">
         <v>150300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>138600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>181100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>117100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>102000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>98300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>95400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>120000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>138300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>158400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>222400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>197100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>236000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>155600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>112600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>98300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>112200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>157800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>158200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>160100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>173700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>197900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>122400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>136200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4008,41 +4110,44 @@
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E47" s="3">
         <v>31300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>18200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>15300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>19900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4064,30 +4169,30 @@
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V47" s="3">
         <v>3900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4100</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB47" s="3">
         <v>2500</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4103,86 +4208,89 @@
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>537600</v>
+      </c>
+      <c r="E48" s="3">
         <v>543400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>707700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>721100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>879600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>957400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>908300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1138700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1144100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1246400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1245000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1262100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1286200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1308700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1335700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1365200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1383600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1407300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1273600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1286000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1237600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1247800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1250800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1239500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1182800</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4198,16 +4306,19 @@
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -4219,65 +4330,65 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>3800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11500</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,86 +4600,89 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E52" s="3">
         <v>50600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>41600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>43300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>86700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>89900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>63400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>63200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>46400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>33500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>21100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9600</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,86 +4796,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>706300</v>
+      </c>
+      <c r="E54" s="3">
         <v>775600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>898500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>962000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1055400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1159500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1115600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1320200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1353400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1434500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1456600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1525000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1519600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1554800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1501900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1495300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1511700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1542000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1451900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1466000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1425300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1444000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1472400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1389600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1342600</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4768,8 +4894,11 @@
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,86 +4968,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E57" s="3">
         <v>54500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>59000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>48500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>51300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>59400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>66800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>76700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>61500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>52800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>70000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>47600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>53200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>39900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>49200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>47800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>49900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>33600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>54300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>44700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>41900</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4933,86 +5064,89 @@
       <c r="AG57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E58" s="3">
         <v>156800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>163600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>124300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>145000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>88800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>97200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>112800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>111700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>111100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>111700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>107700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>104000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>99700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>189300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>176900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>168200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>166100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>165900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>163600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>147100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>149800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>155200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>149900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>144500</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5028,86 +5162,89 @@
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E59" s="3">
         <v>42700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>45400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>48600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>46200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>57900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>61000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>76400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>85000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>115400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>87400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>140600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>110800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>91200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>83200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>82100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>40900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>39000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>40900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>41900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>52300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>33900</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5123,86 +5260,89 @@
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>196800</v>
+      </c>
+      <c r="E60" s="3">
         <v>253900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>267900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>222100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>242100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>186300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>214500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>240300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>249400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>250400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>258200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>276000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>261400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>287900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>353300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>308000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>300600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>295900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>256700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>245900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>226700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>231200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>251400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>246900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>220400</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5218,86 +5358,89 @@
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>299000</v>
+      </c>
+      <c r="E61" s="3">
         <v>315500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>364700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>441900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>463600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>597800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>502500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>523200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>521500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>547400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>539700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>585800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>600100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>624100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>542500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>586900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>619800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>641000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>677400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>717500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>696900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>727800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>760200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>828500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>784500</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5313,86 +5456,89 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E62" s="3">
         <v>63700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>65800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>70000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>74400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>75700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>90400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>133600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>150000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>162200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>170700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>168600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>167300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>158500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>148300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>154900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>150000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>166900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>91900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>89900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>92500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>89700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>86400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>81600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>89100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,86 +5848,89 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>551600</v>
+      </c>
+      <c r="E66" s="3">
         <v>633000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>698400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>734100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>780100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>859700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>807400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>897100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>920800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>960000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>968600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1030300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1028700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1070500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1044100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1049800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1070400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1103800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1026000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1053200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1016000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1048800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1097900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1157000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1093900</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5788,8 +5946,11 @@
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,86 +6374,89 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-117300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-129000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-71100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-42800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>39900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>49000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>164600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>174600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>217400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>231700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>239200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>234900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>229200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>215100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>203700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>200300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>198400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>187400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>175100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>172100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>158900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>139800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>119900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>133400</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6298,8 +6472,11 @@
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,86 +6766,89 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>154700</v>
+      </c>
+      <c r="E76" s="3">
         <v>142600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>200000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>227900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>275200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>299800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>308200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>423000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>432500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>474500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>488000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>494700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>490800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>484300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>457900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>445500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>441400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>438200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>425900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>412700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>409300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>395200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>374500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>232600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>248700</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6678,8 +6864,11 @@
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-57900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-47600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-115600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-42800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>13200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>22600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>15400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>13300</v>
+        <v>9800</v>
       </c>
       <c r="E83" s="3">
         <v>13300</v>
       </c>
       <c r="F83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="G83" s="3">
         <v>15300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>19600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>20600</v>
       </c>
       <c r="R83" s="3">
         <v>20600</v>
       </c>
       <c r="S83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="T83" s="3">
         <v>20500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>20600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>19800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>18500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>17400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>16000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>15600</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>52600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>79300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>71100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>38400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>27000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>38200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>37600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>44300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>25600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>44100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>55800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>22000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>28100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>36000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>22200</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-82500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-19500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-81500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E94" s="3">
         <v>46600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>33300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>47200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>78400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>41700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-77500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-37400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-55600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-38500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-45100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-80700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-38300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-45100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-35000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-25500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-20400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-36700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-39800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>35400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-38300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-38700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>43200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>51300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-32700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>14300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-22900</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-59900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-33700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>82100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>34500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>61600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>22500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>33900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>MESA</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E8" s="3">
         <v>131600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>118800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>114400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>114700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>121800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>147200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>125600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>134400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>123200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>147800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>130800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>125200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>97300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>150400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>108000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>73100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>179900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>184000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>187800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>180200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>177100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>178200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>177500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>171700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>167600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>164700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>157300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>167000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>159100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>160200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>160500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>95000</v>
+        <v>92300</v>
       </c>
       <c r="E9" s="3">
+        <v>95700</v>
+      </c>
+      <c r="F9" s="3">
         <v>101600</v>
       </c>
-      <c r="F9" s="3">
-        <v>106800</v>
-      </c>
       <c r="G9" s="3">
-        <v>103500</v>
+        <v>104500</v>
       </c>
       <c r="H9" s="3">
-        <v>101700</v>
+        <v>104300</v>
       </c>
       <c r="I9" s="3">
+        <v>102500</v>
+      </c>
+      <c r="J9" s="3">
         <v>110700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>98300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>102200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>99200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>118100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>117500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>103900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>100100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>101200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>91300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>68500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>131000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>123300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>124500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>121400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>110000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>108200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>108000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>119100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>142300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>21200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>36600</v>
+        <v>18500</v>
       </c>
       <c r="E10" s="3">
-        <v>17200</v>
+        <v>35900</v>
       </c>
       <c r="F10" s="3">
-        <v>7600</v>
+        <v>17100</v>
       </c>
       <c r="G10" s="3">
-        <v>11200</v>
+        <v>9900</v>
       </c>
       <c r="H10" s="3">
-        <v>20200</v>
+        <v>10400</v>
       </c>
       <c r="I10" s="3">
+        <v>19400</v>
+      </c>
+      <c r="J10" s="3">
         <v>36500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>27300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>32200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>29700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>49200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>48900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>60700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>63300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>58800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>67100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>70000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>69500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>52600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>154000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>22400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>146900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>158600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>137900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>136300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>135300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,88 +1338,91 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-7800</v>
+        <v>10700</v>
       </c>
       <c r="E14" s="3">
-        <v>37400</v>
+        <v>-8600</v>
       </c>
       <c r="F14" s="3">
-        <v>3400</v>
+        <v>35400</v>
       </c>
       <c r="G14" s="3">
-        <v>30500</v>
+        <v>2900</v>
       </c>
       <c r="H14" s="3">
-        <v>16700</v>
+        <v>20900</v>
       </c>
       <c r="I14" s="3">
-        <v>3700</v>
+        <v>14600</v>
       </c>
       <c r="J14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K14" s="3">
         <v>133000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>39500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
-        <v>-26100</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>-26100</v>
       </c>
       <c r="P14" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-51500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-12300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-40800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-43000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>9500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>15100</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1410,8 +1430,8 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1419,92 +1439,95 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>9800</v>
+        <v>8800</v>
       </c>
       <c r="E15" s="3">
-        <v>13300</v>
+        <v>9100</v>
       </c>
       <c r="F15" s="3">
         <v>13300</v>
       </c>
       <c r="G15" s="3">
-        <v>15300</v>
+        <v>15600</v>
       </c>
       <c r="H15" s="3">
-        <v>16500</v>
+        <v>14500</v>
       </c>
       <c r="I15" s="3">
+        <v>15700</v>
+      </c>
+      <c r="J15" s="3">
         <v>15200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>20700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>20900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>20500</v>
-      </c>
-      <c r="R15" s="3">
-        <v>20600</v>
       </c>
       <c r="S15" s="3">
         <v>20600</v>
       </c>
       <c r="T15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="U15" s="3">
         <v>20500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>20600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>20500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>19800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>19300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>18500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>17400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>16000</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD15" s="3">
         <v>15900</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>109400</v>
+        <v>111900</v>
       </c>
       <c r="E17" s="3">
-        <v>167200</v>
+        <v>117300</v>
       </c>
       <c r="F17" s="3">
+        <v>129400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>131100</v>
+      </c>
+      <c r="H17" s="3">
+        <v>131200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>132000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>141000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>262500</v>
+      </c>
+      <c r="L17" s="3">
+        <v>134200</v>
+      </c>
+      <c r="M17" s="3">
+        <v>168000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>151700</v>
+      </c>
+      <c r="O17" s="3">
+        <v>125700</v>
+      </c>
+      <c r="P17" s="3">
+        <v>110800</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>80500</v>
+      </c>
+      <c r="R17" s="3">
+        <v>122400</v>
+      </c>
+      <c r="S17" s="3">
+        <v>84200</v>
+      </c>
+      <c r="T17" s="3">
+        <v>57900</v>
+      </c>
+      <c r="U17" s="3">
+        <v>166000</v>
+      </c>
+      <c r="V17" s="3">
+        <v>156800</v>
+      </c>
+      <c r="W17" s="3">
+        <v>157400</v>
+      </c>
+      <c r="X17" s="3">
+        <v>163100</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>146400</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>138900</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>135700</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>172200</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>151300</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>149700</v>
+      </c>
+      <c r="AE17" s="3">
         <v>134600</v>
       </c>
-      <c r="G17" s="3">
-        <v>154900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>148700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>144700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>262500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>134200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>168000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>151700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>125700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>110800</v>
-      </c>
-      <c r="P17" s="3">
-        <v>80500</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>122400</v>
-      </c>
-      <c r="R17" s="3">
-        <v>84200</v>
-      </c>
-      <c r="S17" s="3">
-        <v>57900</v>
-      </c>
-      <c r="T17" s="3">
-        <v>166000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>156800</v>
-      </c>
-      <c r="V17" s="3">
-        <v>157400</v>
-      </c>
-      <c r="W17" s="3">
-        <v>163100</v>
-      </c>
-      <c r="X17" s="3">
-        <v>146400</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>138900</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>135700</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>172200</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>151300</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>149700</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>134600</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>130600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>138700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>139400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>22200</v>
+        <v>-1100</v>
       </c>
       <c r="E18" s="3">
-        <v>-48400</v>
+        <v>14300</v>
       </c>
       <c r="F18" s="3">
-        <v>-20200</v>
+        <v>-10600</v>
       </c>
       <c r="G18" s="3">
-        <v>-40200</v>
+        <v>-16700</v>
       </c>
       <c r="H18" s="3">
-        <v>-26900</v>
+        <v>-16500</v>
       </c>
       <c r="I18" s="3">
-        <v>2500</v>
+        <v>-10100</v>
       </c>
       <c r="J18" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-136900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-44800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>23800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>27200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>30400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>30700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>39300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>41800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>22700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>36400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>20800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,288 +1815,295 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="H20" s="3">
+        <v>900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
-        <v>100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
-        <v>300</v>
-      </c>
-      <c r="X20" s="3">
-        <v>400</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>600</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-13300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-12500</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-11900</v>
       </c>
       <c r="AF20" s="3">
         <v>-11900</v>
       </c>
       <c r="AG20" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>32200</v>
+        <v>7800</v>
       </c>
       <c r="E21" s="3">
-        <v>-32500</v>
+        <v>22900</v>
       </c>
       <c r="F21" s="3">
-        <v>-4400</v>
+        <v>2800</v>
       </c>
       <c r="G21" s="3">
-        <v>-23000</v>
+        <v>800</v>
       </c>
       <c r="H21" s="3">
-        <v>-7600</v>
+        <v>-2900</v>
       </c>
       <c r="I21" s="3">
-        <v>16500</v>
+        <v>6200</v>
       </c>
       <c r="J21" s="3">
+        <v>21800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-118500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>35400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>37000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>48500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>44600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>35900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>35300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>47500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>51100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>37100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>50400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>58400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>59300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>15500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>30900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>26000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>40100</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E22" s="3">
         <v>10600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>14100</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>14100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E23" s="3">
         <v>11700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-57000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-31300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-50300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-37200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-148600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-55200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>18900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>17100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>25000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>26600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>24500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-33000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-12400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E26" s="3">
         <v>11700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-57900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-47600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-35100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-115600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-42800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>12200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>13200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E27" s="3">
         <v>11700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-57900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-47600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-35100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-115600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-42800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>12200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>13200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>15400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2717,8 +2778,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2735,21 +2796,21 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>600</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="3">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>21400</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>200</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N32" s="3">
+        <v>6500</v>
+      </c>
+      <c r="O32" s="3">
+        <v>6700</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>400</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>6500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>6700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V32" s="3">
+        <v>200</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="U32" s="3">
-        <v>200</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>13300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>12500</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>11900</v>
       </c>
       <c r="AF32" s="3">
         <v>11900</v>
       </c>
       <c r="AG32" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AH32" s="3">
         <v>10200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E33" s="3">
         <v>11700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-57900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-47600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-35100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-115600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-42800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>12200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>13200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>22600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>15400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E35" s="3">
         <v>11700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-57900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-47600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-35100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-115600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-42800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>12200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>13200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>22600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>15400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,89 +3611,90 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E41" s="3">
         <v>18500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>48300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>51400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>56100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>57700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>54400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>75900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>102300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>120500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>180400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>147900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>181300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>99400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>64900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>52400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>68900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>79900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>77700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>88600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>103300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>41700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>52700</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3623,13 +3710,16 @@
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3692,14 +3782,14 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>15000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>19900</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3712,8 +3802,8 @@
       <c r="AE42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -3721,89 +3811,92 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>14200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>24100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>23100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>21600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>17000</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3819,58 +3912,61 @@
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E44" s="3">
         <v>29500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>28800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>29200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>28700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>26700</v>
-      </c>
-      <c r="K44" s="3">
-        <v>26300</v>
       </c>
       <c r="L44" s="3">
         <v>26300</v>
       </c>
       <c r="M44" s="3">
+        <v>26300</v>
+      </c>
+      <c r="N44" s="3">
         <v>25200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>24700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>23000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>22800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>23000</v>
-      </c>
-      <c r="S44" s="3">
-        <v>22400</v>
       </c>
       <c r="T44" s="3">
         <v>22400</v>
@@ -3879,29 +3975,29 @@
         <v>22400</v>
       </c>
       <c r="V44" s="3">
+        <v>22400</v>
+      </c>
+      <c r="W44" s="3">
         <v>21300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>20300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>19200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>17400</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>15700</v>
       </c>
       <c r="AA44" s="3">
         <v>15700</v>
       </c>
       <c r="AB44" s="3">
+        <v>15700</v>
+      </c>
+      <c r="AC44" s="3">
         <v>15400</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3917,89 +4013,92 @@
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>45800</v>
+        <v>20200</v>
       </c>
       <c r="E45" s="3">
-        <v>99900</v>
+        <v>39100</v>
       </c>
       <c r="F45" s="3">
-        <v>68100</v>
+        <v>92400</v>
       </c>
       <c r="G45" s="3">
-        <v>100500</v>
+        <v>58800</v>
       </c>
       <c r="H45" s="3">
-        <v>29000</v>
+        <v>91300</v>
       </c>
       <c r="I45" s="3">
-        <v>7300</v>
+        <v>19700</v>
       </c>
       <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>10000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>12300</v>
       </c>
       <c r="P45" s="3">
         <v>12300</v>
       </c>
       <c r="Q45" s="3">
+        <v>12300</v>
+      </c>
+      <c r="R45" s="3">
         <v>16500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>44600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>50100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>51100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>46700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>43300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>51000</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4015,89 +4114,92 @@
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E46" s="3">
         <v>98400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>150300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>138600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>181100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>117100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>102000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>98300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>95400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>120000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>138300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>158400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>222400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>197100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>236000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>155600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>112600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>98300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>112200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>157800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>158200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>160100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>173700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>197900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>122400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>136200</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4113,44 +4215,47 @@
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>19200</v>
+        <v>300</v>
       </c>
       <c r="E47" s="3">
-        <v>31300</v>
+        <v>11400</v>
       </c>
       <c r="F47" s="3">
+        <v>23000</v>
+      </c>
+      <c r="G47" s="3">
         <v>20300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>15300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>19000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4172,30 +4277,30 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W47" s="3">
         <v>3900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4100</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC47" s="3">
         <v>2500</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4211,89 +4316,92 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>505200</v>
+      </c>
+      <c r="E48" s="3">
         <v>537600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>543400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>707700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>721100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>879600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>957400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>908300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1138700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1144100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1246400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1245000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1262100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1286200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1308700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1335700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1365200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1383600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1407300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1273600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1286000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1237600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1247800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1250800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1239500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1182800</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4309,16 +4417,19 @@
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -4333,65 +4444,65 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>3800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11500</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,89 +4720,92 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>51100</v>
+        <v>59900</v>
       </c>
       <c r="E52" s="3">
-        <v>50600</v>
+        <v>44700</v>
       </c>
       <c r="F52" s="3">
-        <v>31800</v>
+        <v>43400</v>
       </c>
       <c r="G52" s="3">
-        <v>41600</v>
+        <v>15100</v>
       </c>
       <c r="H52" s="3">
-        <v>43300</v>
+        <v>23700</v>
       </c>
       <c r="I52" s="3">
-        <v>86700</v>
+        <v>24200</v>
       </c>
       <c r="J52" s="3">
+        <v>76400</v>
+      </c>
+      <c r="K52" s="3">
         <v>89900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>63400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>63200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>46400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>33500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>21100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9600</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,89 +4922,92 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>664400</v>
+      </c>
+      <c r="E54" s="3">
         <v>706300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>775600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>898500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>962000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1055400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1159500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1115600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1320200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1353400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1434500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1456600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1525000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1519600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1554800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1501900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1495300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1511700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1542000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1451900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1466000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1425300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1444000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1472400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1389600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1342600</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,89 +5099,90 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E57" s="3">
         <v>57300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>54500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>51900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>48500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>51300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>66800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>76700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>61500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>52800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>70000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>47600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>53200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>49200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>47800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>49900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>33600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>40500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>40400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>54300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>44700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>41900</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5067,89 +5198,92 @@
       <c r="AH57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>94400</v>
+        <v>75000</v>
       </c>
       <c r="E58" s="3">
-        <v>156800</v>
+        <v>96700</v>
       </c>
       <c r="F58" s="3">
+        <v>160000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>167100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>128700</v>
+      </c>
+      <c r="I58" s="3">
+        <v>150600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>94200</v>
+      </c>
+      <c r="K58" s="3">
+        <v>97200</v>
+      </c>
+      <c r="L58" s="3">
+        <v>112800</v>
+      </c>
+      <c r="M58" s="3">
+        <v>111700</v>
+      </c>
+      <c r="N58" s="3">
+        <v>111100</v>
+      </c>
+      <c r="O58" s="3">
+        <v>111700</v>
+      </c>
+      <c r="P58" s="3">
+        <v>107700</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>104000</v>
+      </c>
+      <c r="R58" s="3">
+        <v>99700</v>
+      </c>
+      <c r="S58" s="3">
+        <v>189300</v>
+      </c>
+      <c r="T58" s="3">
+        <v>176900</v>
+      </c>
+      <c r="U58" s="3">
+        <v>168200</v>
+      </c>
+      <c r="V58" s="3">
+        <v>166100</v>
+      </c>
+      <c r="W58" s="3">
+        <v>165900</v>
+      </c>
+      <c r="X58" s="3">
         <v>163600</v>
       </c>
-      <c r="G58" s="3">
-        <v>124300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>145000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>88800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>97200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>112800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>111700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>111100</v>
-      </c>
-      <c r="N58" s="3">
-        <v>111700</v>
-      </c>
-      <c r="O58" s="3">
-        <v>107700</v>
-      </c>
-      <c r="P58" s="3">
-        <v>104000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>99700</v>
-      </c>
-      <c r="R58" s="3">
-        <v>189300</v>
-      </c>
-      <c r="S58" s="3">
-        <v>176900</v>
-      </c>
-      <c r="T58" s="3">
-        <v>168200</v>
-      </c>
-      <c r="U58" s="3">
-        <v>166100</v>
-      </c>
-      <c r="V58" s="3">
-        <v>165900</v>
-      </c>
-      <c r="W58" s="3">
-        <v>163600</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>147100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>149800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>155200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>149900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>144500</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5165,89 +5299,92 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>45100</v>
+        <v>4400</v>
       </c>
       <c r="E59" s="3">
-        <v>42700</v>
+        <v>2800</v>
       </c>
       <c r="F59" s="3">
-        <v>45400</v>
+        <v>4000</v>
       </c>
       <c r="G59" s="3">
-        <v>45900</v>
+        <v>5000</v>
       </c>
       <c r="H59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K59" s="3">
+        <v>57900</v>
+      </c>
+      <c r="L59" s="3">
+        <v>60700</v>
+      </c>
+      <c r="M59" s="3">
+        <v>61000</v>
+      </c>
+      <c r="N59" s="3">
+        <v>76400</v>
+      </c>
+      <c r="O59" s="3">
+        <v>85000</v>
+      </c>
+      <c r="P59" s="3">
+        <v>115400</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>87400</v>
+      </c>
+      <c r="R59" s="3">
+        <v>140600</v>
+      </c>
+      <c r="S59" s="3">
+        <v>110800</v>
+      </c>
+      <c r="T59" s="3">
+        <v>91200</v>
+      </c>
+      <c r="U59" s="3">
+        <v>83200</v>
+      </c>
+      <c r="V59" s="3">
+        <v>82100</v>
+      </c>
+      <c r="W59" s="3">
+        <v>40900</v>
+      </c>
+      <c r="X59" s="3">
         <v>48600</v>
       </c>
-      <c r="I59" s="3">
-        <v>46200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>57900</v>
-      </c>
-      <c r="K59" s="3">
-        <v>60700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>61000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>76400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>85000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>115400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>87400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>140600</v>
-      </c>
-      <c r="R59" s="3">
-        <v>110800</v>
-      </c>
-      <c r="S59" s="3">
-        <v>91200</v>
-      </c>
-      <c r="T59" s="3">
-        <v>83200</v>
-      </c>
-      <c r="U59" s="3">
-        <v>82100</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="Y59" s="3">
+        <v>39000</v>
+      </c>
+      <c r="Z59" s="3">
         <v>40900</v>
       </c>
-      <c r="W59" s="3">
-        <v>48600</v>
-      </c>
-      <c r="X59" s="3">
-        <v>39000</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>40900</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>41900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>52300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>33900</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5263,89 +5400,92 @@
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>187500</v>
+      </c>
+      <c r="E60" s="3">
         <v>196800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>253900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>267900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>222100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>242100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>186300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>214500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>240300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>249400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>250400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>258200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>276000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>261400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>287900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>353300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>308000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>300600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>295900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>256700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>245900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>226700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>231200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>251400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>246900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>220400</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5361,89 +5501,92 @@
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>299000</v>
+        <v>294200</v>
       </c>
       <c r="E61" s="3">
-        <v>315500</v>
+        <v>306300</v>
       </c>
       <c r="F61" s="3">
-        <v>364700</v>
+        <v>323200</v>
       </c>
       <c r="G61" s="3">
-        <v>441900</v>
+        <v>372800</v>
       </c>
       <c r="H61" s="3">
-        <v>463600</v>
+        <v>450900</v>
       </c>
       <c r="I61" s="3">
-        <v>597800</v>
+        <v>472100</v>
       </c>
       <c r="J61" s="3">
+        <v>607300</v>
+      </c>
+      <c r="K61" s="3">
         <v>502500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>523200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>521500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>547400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>539700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>585800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>600100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>624100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>542500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>586900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>619800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>641000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>677400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>717500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>696900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>727800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>760200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>828500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>784500</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5459,89 +5602,92 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>55800</v>
+        <v>31400</v>
       </c>
       <c r="E62" s="3">
-        <v>63700</v>
+        <v>31800</v>
       </c>
       <c r="F62" s="3">
-        <v>65800</v>
+        <v>32600</v>
       </c>
       <c r="G62" s="3">
-        <v>70000</v>
+        <v>32700</v>
       </c>
       <c r="H62" s="3">
-        <v>74400</v>
+        <v>32600</v>
       </c>
       <c r="I62" s="3">
-        <v>75700</v>
+        <v>31400</v>
       </c>
       <c r="J62" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K62" s="3">
         <v>90400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>133600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>150000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>162200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>170700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>168600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>167300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>158500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>148300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>154900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>150000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>166900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>91900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>89900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>92500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>89700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>86400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>81600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>89100</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,89 +6006,92 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>529500</v>
+      </c>
+      <c r="E66" s="3">
         <v>551600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>633000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>698400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>734100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>780100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>859700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>807400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>897100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>920800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>960000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>968600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1030300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1028700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1070500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1044100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1049800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1070400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1103800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1026000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1053200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1016000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1048800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1097900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1157000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1093900</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,89 +6548,92 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-137200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-117300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-129000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-71100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-42800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>39900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>49000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>164600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>174600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>217400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>231700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>239200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>234900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>229200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>215100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>203700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>200300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>198400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>187400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>175100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>172100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>158900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>139800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>119900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>133400</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,89 +6952,92 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E76" s="3">
         <v>154700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>142600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>200000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>227900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>275200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>299800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>308200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>423000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>432500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>474500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>488000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>494700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>490800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>484300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>457900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>445500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>441400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>438200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>425900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>412700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>409300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>395200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>374500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>232600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>248700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E81" s="3">
         <v>11700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-57900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-47600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-35100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-115600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-42800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>12200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>13200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>22600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>15400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>9800</v>
+        <v>15300</v>
       </c>
       <c r="E83" s="3">
-        <v>13300</v>
+        <v>17300</v>
       </c>
       <c r="F83" s="3">
-        <v>13300</v>
+        <v>14400</v>
       </c>
       <c r="G83" s="3">
-        <v>15300</v>
+        <v>19400</v>
       </c>
       <c r="H83" s="3">
-        <v>16500</v>
+        <v>19800</v>
       </c>
       <c r="I83" s="3">
-        <v>15200</v>
+        <v>20500</v>
       </c>
       <c r="J83" s="3">
+        <v>20700</v>
+      </c>
+      <c r="K83" s="3">
         <v>19600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>20600</v>
       </c>
       <c r="S83" s="3">
         <v>20600</v>
       </c>
       <c r="T83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="U83" s="3">
         <v>20500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>19300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>18500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>17400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>16000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>15800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>15600</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E89" s="3">
         <v>16200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>52600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>79300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>71100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>38400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>27000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>38200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>37600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>44300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>25600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>44100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>55800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>22000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>13100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>28100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>36000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>22200</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-82500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-19500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-81500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E94" s="3">
         <v>47900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>46600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>33300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>47200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>78400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>41700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-77500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-20300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-37400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-84200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8585,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,129 +8987,135 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-61800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-55600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-38500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-45100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-80700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>21000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-38300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-45100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-23100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-35000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-25500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-20400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-36700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-39800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>35400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-38300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-38700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>43200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>51300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-32700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>14300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-22900</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E102" s="3">
         <v>2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-21500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-59900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>32500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-33700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>82100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>34500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>61600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>33900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>MESA</t>
   </si>
@@ -656,454 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>115300</v>
+      </c>
+      <c r="F8" s="3">
         <v>110800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>131600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>118800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>114400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>114700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>121800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>147200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>125600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>134400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>123200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>147800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>130800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>125200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>97300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>150400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>108000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>73100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>179900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>184000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>187800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>180200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>177100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>178200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>177500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>171700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>167600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>164700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>157300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>167000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>159100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>160200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>160500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>88900</v>
+      </c>
+      <c r="F9" s="3">
         <v>92300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>95700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>101600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>104500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>104300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>102500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>110700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>98300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>102200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>99200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>118100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>117500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>103900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>100100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>101200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>91300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>68500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>131000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>123300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>124500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>121400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>110000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>108200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>108000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>119100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>13600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>142300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>10400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>8400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>21200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>23900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>26300</v>
+      </c>
+      <c r="F10" s="3">
         <v>18500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>35900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>17100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>9900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>10400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>19400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>36500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>27300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>32200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>24000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>29700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>13300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>21300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>-2800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>49200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>16700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>4600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>48900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>60700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>63300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>58800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>67100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>70000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>69500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>52600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>154000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>22400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>146900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>158600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>137900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>136300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>135300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1164,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1267,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,165 +1374,177 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>21800</v>
+      </c>
+      <c r="F14" s="3">
         <v>10700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-8600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>35400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>20900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>14600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>5400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>133000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>39500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-26100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-51500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-12300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-40800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-43000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>9500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>3600</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>15100</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F15" s="3">
         <v>8800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>9100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>13300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>15600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>14500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>15700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>15200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>19600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>20100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>20700</v>
-      </c>
-      <c r="N15" s="3">
-        <v>21000</v>
       </c>
       <c r="O15" s="3">
         <v>20700</v>
       </c>
       <c r="P15" s="3">
-        <v>20900</v>
+        <v>21000</v>
       </c>
       <c r="Q15" s="3">
         <v>20700</v>
       </c>
       <c r="R15" s="3">
+        <v>20900</v>
+      </c>
+      <c r="S15" s="3">
+        <v>20700</v>
+      </c>
+      <c r="T15" s="3">
         <v>20500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>20600</v>
-      </c>
-      <c r="T15" s="3">
-        <v>20600</v>
-      </c>
-      <c r="U15" s="3">
-        <v>20500</v>
       </c>
       <c r="V15" s="3">
         <v>20600</v>
@@ -1508,32 +1553,32 @@
         <v>20500</v>
       </c>
       <c r="X15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>20500</v>
+      </c>
+      <c r="Z15" s="3">
         <v>19800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>19300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>18500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>17400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>16000</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF15" s="3">
         <v>15900</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1543,8 +1588,14 @@
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1628,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>101700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>109000</v>
+      </c>
+      <c r="F17" s="3">
         <v>111900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>117300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>129400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>131100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>131200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>132000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>141000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>262500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>134200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>168000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>151700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>125700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>110800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>80500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>122400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>84200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>57900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>166000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>156800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>157400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>163100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>146400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>138900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>135700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>172200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>151300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>149700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>134600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>130600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>138700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>139400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>14300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-10600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-16700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-16500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-10100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>6200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-136900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-44800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>5100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>14400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>16800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>28000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>23800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>15200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>13900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>27200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>30400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>17100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>30700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>39300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>41800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>16300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>15000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>22700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>36400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>20400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>20800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,290 +1881,304 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-6500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-6700</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F21" s="3">
         <v>7800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>22900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>6200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>21800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-118500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>16300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-26300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>10600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>19100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>35400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>37000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>48500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>44600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>35900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>35300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>47500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>51100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>37100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>50400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>58400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>59300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>15500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>18600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>30900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>26000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>40100</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F22" s="3">
         <v>9000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>10600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>11200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>13600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>12000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>13000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>11300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>10500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>8700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>8100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>7900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>8300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>8600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>8800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>9100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>9500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>10400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>11700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>12600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>13600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>13500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>13800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>14800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>15300</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>14100</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD22" s="3">
         <v>14100</v>
@@ -2107,8 +2186,8 @@
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>8</v>
+      <c r="AF22" s="3">
+        <v>14100</v>
       </c>
       <c r="AG22" s="3" t="s">
         <v>8</v>
@@ -2119,210 +2198,228 @@
       <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-116300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-20700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>11700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-57000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-31300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-50300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-37200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-10000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-148600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-12500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-55200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-18400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-9900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>5800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>7600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>18900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>14500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>4900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>14300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>17100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>3900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>17300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>25000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>26600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>3000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>10200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>24500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>8500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>10600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-2800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-33000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-12400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-4100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>4800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>3200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>3500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>4800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>4100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>5900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>7900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>4700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>9100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>3200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>3900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2519,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-114600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-19900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>11700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-57900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-28300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-47600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-35100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-9100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-115600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-10000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-42800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-7500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>4300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>5700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>14100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>11400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>3400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>10800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>12200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>13200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>19100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>18800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>2400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>1200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>5500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>15400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>5300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>6600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-114600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-19900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>11700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-57900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-28300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-47600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-35100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-9100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-115600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-10000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-42800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-7500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>5700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>14100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>11400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>3400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>10800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>12200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>13200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>19100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>18800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>1200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>5500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>15400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>5300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>6600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2840,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2781,11 +2902,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2799,24 +2920,24 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>600</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>21400</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2826,8 +2947,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3054,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3161,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>6500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>6700</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>13300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>12500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>11900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>11900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>10200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-114600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-19900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>11700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-57900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-28300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-47600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-35100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-9100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-115600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-10000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-42800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-7500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>5700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>14100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>11400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>3400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>10800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>12200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>13200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>19100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>19400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>22600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>5500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>15400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>5300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>6600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3482,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-114600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-19900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>11700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-57900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-28300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-47600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-35100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-9100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-115600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-10000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-42800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-7500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>5700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>14100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>11400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>3400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>10800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>12200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>13200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>19100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>19400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>22600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>5500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>15400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>5300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>6600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3744,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,95 +3783,97 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15600</v>
+      </c>
+      <c r="F41" s="3">
         <v>16300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>18500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>32900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>48300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>51400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>56100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>57700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>54400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>75900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>102300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>120500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>180400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>147900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>181300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>99400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>64900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>52400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>57800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>68900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>79900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>77700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>88600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>103300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>41700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>52700</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3713,20 +3886,26 @@
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>5400</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -3785,17 +3964,17 @@
         <v>0</v>
       </c>
       <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>15000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>19900</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3805,104 +3984,110 @@
       <c r="AF42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="3">
-        <v>0</v>
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F43" s="3">
         <v>6000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>8300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>9900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>13100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>6800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>13900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>15400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>13700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>14600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>14200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>24100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>23100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>7900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>12100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>6000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>14300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>21600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>17000</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3915,95 +4100,101 @@
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>28300</v>
+      </c>
+      <c r="F44" s="3">
         <v>30700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>29500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>28800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>29200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>28700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>26800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>25500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>26700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>26300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>26300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>25200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>24500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>24700</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>23000</v>
-      </c>
-      <c r="R44" s="3">
-        <v>22800</v>
       </c>
       <c r="S44" s="3">
         <v>23000</v>
       </c>
       <c r="T44" s="3">
-        <v>22400</v>
+        <v>22800</v>
       </c>
       <c r="U44" s="3">
-        <v>22400</v>
+        <v>23000</v>
       </c>
       <c r="V44" s="3">
         <v>22400</v>
       </c>
       <c r="W44" s="3">
+        <v>22400</v>
+      </c>
+      <c r="X44" s="3">
+        <v>22400</v>
+      </c>
+      <c r="Y44" s="3">
         <v>21300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>20300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>19200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>17400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>15700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>15700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>15400</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4016,95 +4207,101 @@
       <c r="AI44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F45" s="3">
         <v>20200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>39100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>92400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>58800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>91300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>19700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>10000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>10600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>7800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>10200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>12300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>12300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>16500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>19500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>10600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>9400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>8000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>44600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>50100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>51100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>46700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>44700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>43300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>51000</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4117,95 +4314,101 @@
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>160700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>61300</v>
+      </c>
+      <c r="F46" s="3">
         <v>84900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>98400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>150300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>138600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>181100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>117100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>102000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>98300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>95400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>120000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>138300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>158400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>222400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>197100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>236000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>155600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>112600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>98300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>112200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>157800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>158200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>160100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>173700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>197900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>122400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>136200</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4218,50 +4421,56 @@
       <c r="AI46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>11400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>23000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>20300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>18200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>15300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>13400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>15200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>16600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>19900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>19000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4280,33 +4489,33 @@
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y47" s="3">
         <v>3900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>4500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>5000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>4100</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE47" s="3">
         <v>2500</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4319,95 +4528,101 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>210200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>433600</v>
+      </c>
+      <c r="F48" s="3">
         <v>505200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>537600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>543400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>707700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>721100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>879600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>957400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>908300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1138700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1144100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1246400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1245000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1262100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1286200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1308700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1335700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1365200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1383600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1407300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1273600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1286000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1237600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1247800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1250800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1239500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1182800</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4420,8 +4635,14 @@
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4447,68 +4668,68 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>3800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>6000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>6300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>6500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>6800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>7100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>7400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>7700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>8000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>8400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>8800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>9200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>9500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>10000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>10400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>10900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>11300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>11400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>11500</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4521,8 +4742,14 @@
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4849,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,95 +4956,101 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>95600</v>
+      </c>
+      <c r="F52" s="3">
         <v>59900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>44700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>43400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>15100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>23700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>24200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>76400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>89900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>63400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>63200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>24300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>46400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>33500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>28900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>9100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>21100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>13300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>7100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>7300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>12100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>7500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>12300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>16200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>9600</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4824,8 +5063,14 @@
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,95 +5170,101 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>383600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>596900</v>
+      </c>
+      <c r="F54" s="3">
         <v>664400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>706300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>775600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>898500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>962000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1055400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1159500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1115600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1320200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1353400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1434500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1456600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1525000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1519600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1554800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1501900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1495300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1511700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1542000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1451900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1466000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1425300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1444000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1472400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1389600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1342600</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5026,8 +5277,14 @@
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5320,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,95 +5359,97 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>72100</v>
+      </c>
+      <c r="F57" s="3">
         <v>64400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>57300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>54500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>59000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>51900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>48500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>51300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>59400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>66800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>76700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>62900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>61500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>52800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>70000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>47600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>53200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>39900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>49200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>47800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>49900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>33600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>40500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>40400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>54300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>44700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>41900</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5201,95 +5462,101 @@
       <c r="AI57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>144700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>52100</v>
+      </c>
+      <c r="F58" s="3">
         <v>75000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>96700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>160000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>167100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>128700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>150600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>94200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>97200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>112800</v>
-      </c>
-      <c r="M58" s="3">
-        <v>111700</v>
-      </c>
-      <c r="N58" s="3">
-        <v>111100</v>
       </c>
       <c r="O58" s="3">
         <v>111700</v>
       </c>
       <c r="P58" s="3">
+        <v>111100</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>111700</v>
+      </c>
+      <c r="R58" s="3">
         <v>107700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>104000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>99700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>189300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>176900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>168200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>166100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>165900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>163600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>147100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>149800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>155200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>149900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>144500</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5302,95 +5569,101 @@
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F59" s="3">
         <v>4400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>57900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>60700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>61000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>76400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>85000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>115400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>87400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>140600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>110800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>91200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>83200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>82100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>40900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>48600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>39000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>40900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>41900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>52300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>33900</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5403,95 +5676,101 @@
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>253100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>174500</v>
+      </c>
+      <c r="F60" s="3">
         <v>187500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>196800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>253900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>267900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>222100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>242100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>186300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>214500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>240300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>249400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>250400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>258200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>276000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>261400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>287900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>353300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>308000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>300600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>295900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>256700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>245900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>226700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>231200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>251400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>246900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>220400</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5504,95 +5783,101 @@
       <c r="AI60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>266700</v>
+      </c>
+      <c r="F61" s="3">
         <v>294200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>306300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>323200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>372800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>450900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>472100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>607300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>502500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>523200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>521500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>547400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>539700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>585800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>600100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>624100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>542500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>586900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>619800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>641000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>677400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>717500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>696900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>727800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>760200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>828500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>784500</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5605,95 +5890,101 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>31600</v>
+      </c>
+      <c r="F62" s="3">
         <v>31400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>31800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>32600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>32700</v>
       </c>
       <c r="H62" s="3">
         <v>32600</v>
       </c>
       <c r="I62" s="3">
+        <v>32700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>32600</v>
+      </c>
+      <c r="K62" s="3">
         <v>31400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>31000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>90400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>133600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>150000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>162200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>170700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>168600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>167300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>158500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>148300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>154900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>150000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>166900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>91900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>89900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>92500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>89700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>86400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>81600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>89100</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5706,8 +5997,14 @@
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6104,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6211,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,95 +6318,101 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>387600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>486600</v>
+      </c>
+      <c r="F66" s="3">
         <v>529500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>551600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>633000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>698400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>734100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>780100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>859700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>807400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>897100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>920800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>960000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>968600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1030300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1028700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1070500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1044100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1049800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1070400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1103800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1026000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1053200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1016000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1048800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1097900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1157000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1093900</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6110,8 +6425,14 @@
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6468,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6571,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6678,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6785,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,95 +6892,101 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-276700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-162100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-137200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-117300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-129000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-71100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-42800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>39900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>49000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>164600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>174600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>217400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>231700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>239200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>234900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>229200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>215100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>203700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>200300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>198400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>187400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>175100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>172100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>158900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>139800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>119900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>133400</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
@@ -6652,8 +6999,14 @@
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7106,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7213,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,95 +7320,101 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>110200</v>
+      </c>
+      <c r="F76" s="3">
         <v>134900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>154700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>142600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>200000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>227900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>275200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>299800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>308200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>423000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>432500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>474500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>488000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>494700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>490800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>484300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>457900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>445500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>441400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>438200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>425900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>412700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>409300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>395200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>374500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>232600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>248700</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7056,8 +7427,14 @@
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7534,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-114600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-19900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>11700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-57900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-28300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-47600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-35100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-9100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-115600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-10000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-42800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-7500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>5700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>14100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>11400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>3400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>10800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>12200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>13200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>19100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>19400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>22600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>5500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>15400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>5300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>6600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,64 +7796,66 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F83" s="3">
         <v>15300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>17300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>14400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>19400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>19800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>20500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>20700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>19600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>20100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>20700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>21000</v>
       </c>
       <c r="O83" s="3">
         <v>20700</v>
       </c>
       <c r="P83" s="3">
-        <v>20900</v>
+        <v>21000</v>
       </c>
       <c r="Q83" s="3">
         <v>20700</v>
       </c>
       <c r="R83" s="3">
+        <v>20900</v>
+      </c>
+      <c r="S83" s="3">
+        <v>20700</v>
+      </c>
+      <c r="T83" s="3">
         <v>20500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>20600</v>
-      </c>
-      <c r="T83" s="3">
-        <v>20600</v>
-      </c>
-      <c r="U83" s="3">
-        <v>20500</v>
       </c>
       <c r="V83" s="3">
         <v>20600</v>
@@ -7467,43 +7864,49 @@
         <v>20500</v>
       </c>
       <c r="X83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="Z83" s="3">
         <v>19800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>19300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>18500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>17400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>16000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>15700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>15900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>15800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>15600</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8006,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8113,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8220,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8327,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8434,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F89" s="3">
         <v>11200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>16200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-7800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-10300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>4800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>52600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>79300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>71100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>38400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>27000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>38200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>37600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>44300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>25600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>44100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>55800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>22000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>13100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>28100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>36000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>22200</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8584,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-6300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-6900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-7800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-16700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-10400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-26700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-6400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-3500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-1500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-12200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-10100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-8600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-82500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-19500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-81500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8794,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8901,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>35900</v>
+      </c>
+      <c r="F94" s="3">
         <v>18400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>47900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>46600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>33300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>47200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>78400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-16600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>41700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-10400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-26900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-16400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-9900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-11900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-12800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-8800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-77500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>1800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-37400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-84200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +9051,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,11 +9079,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +9154,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9261,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9368,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,109 +9475,121 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-79900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-51200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-31900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-61800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-55600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-38500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-45100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-80700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>21000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-38300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-14700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-28600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>4000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-45100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-23100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>4600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-35000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-25500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-20400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-36700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-39800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>35400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-38300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-38700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>43200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>51300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-32700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>4600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>14300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-22900</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,11 +9614,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9192,105 +9689,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-16900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-15400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-21500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-26400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-18200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-59900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>32500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-33700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>82100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>34500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>12500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-5400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-11300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-11100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>2200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>61600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>22500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>33900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MESA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>MESA</t>
   </si>
@@ -656,479 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>94700</v>
+      </c>
+      <c r="F8" s="3">
         <v>103200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>115300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>110800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>131600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>118800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>114400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>114700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>121800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>147200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>125600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>134400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>123200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>147800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>130800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>125200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>97300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>150400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>108000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>73100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>179900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>184000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>187800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>180200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>177100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>178200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>177500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>171700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>167600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>164700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>157300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>167000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>159100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>160200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>160500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>81100</v>
+      </c>
+      <c r="F9" s="3">
         <v>83400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>88900</v>
       </c>
-      <c r="F9" s="3">
-        <v>92300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>95700</v>
-      </c>
       <c r="H9" s="3">
+        <v>92200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J9" s="3">
         <v>101600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>104500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>104300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>102500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>110700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>98300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>102200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>99200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>118100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>117500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>103900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>100100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>101200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>91300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>68500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>131000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>123300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>124500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>121400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>110000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>108200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>108000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>119100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>13600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>142300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>10400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>8400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>21200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>23900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>25200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F10" s="3">
         <v>19800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>26300</v>
       </c>
-      <c r="F10" s="3">
-        <v>18500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>35900</v>
-      </c>
       <c r="H10" s="3">
+        <v>18600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>36600</v>
+      </c>
+      <c r="J10" s="3">
         <v>17100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>9900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>10400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>19400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>36500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>27300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>32200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>24000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>29700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>13300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>21300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-2800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>49200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>16700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>4600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>48900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>60700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>63300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>58800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>67100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>70000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>69500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>52600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>154000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>22400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>146900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>158600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>137900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>136300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>135300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1192,10 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1301,14 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,177 +1414,189 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>53900</v>
+      </c>
+      <c r="F14" s="3">
         <v>107900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>21800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>10700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-8600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>35400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>20900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>14600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>5400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>133000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>39500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-26100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-26100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-51500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-12300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-40800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-43000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>9500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>3600</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>15100</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F15" s="3">
         <v>8000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>7200</v>
       </c>
-      <c r="F15" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>9100</v>
-      </c>
       <c r="H15" s="3">
+        <v>8900</v>
+      </c>
+      <c r="I15" s="3">
+        <v>9800</v>
+      </c>
+      <c r="J15" s="3">
         <v>13300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>15600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>14500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>15700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>15200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>19600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>20100</v>
-      </c>
-      <c r="O15" s="3">
-        <v>20700</v>
-      </c>
-      <c r="P15" s="3">
-        <v>21000</v>
       </c>
       <c r="Q15" s="3">
         <v>20700</v>
       </c>
       <c r="R15" s="3">
-        <v>20900</v>
+        <v>21000</v>
       </c>
       <c r="S15" s="3">
         <v>20700</v>
       </c>
       <c r="T15" s="3">
+        <v>20900</v>
+      </c>
+      <c r="U15" s="3">
+        <v>20700</v>
+      </c>
+      <c r="V15" s="3">
         <v>20500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>20600</v>
-      </c>
-      <c r="V15" s="3">
-        <v>20600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>20500</v>
       </c>
       <c r="X15" s="3">
         <v>20600</v>
@@ -1559,32 +1605,32 @@
         <v>20500</v>
       </c>
       <c r="Z15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>20500</v>
+      </c>
+      <c r="AB15" s="3">
         <v>19800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>19300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>18500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>17400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>16000</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH15" s="3">
         <v>15900</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1594,8 +1640,14 @@
       <c r="AK15" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM15" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1682,236 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>98100</v>
+      </c>
+      <c r="F17" s="3">
         <v>101700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>109000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>111900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>117300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>129400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>131100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>131200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>132000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>141000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>262500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>134200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>168000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>151700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>125700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>110800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>80500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>122400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>84200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>57900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>166000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>156800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>157400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>163100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>146400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>138900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>135700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>172200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>151300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>149700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>134600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>130600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>138700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>139400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>143100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F18" s="3">
         <v>1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>6300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>14300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-10600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-16700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-16500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-10100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>6200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-136900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-44800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>5100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>14400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>16800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>28000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>23800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>15200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>13900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>27200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>30400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>17100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>30700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>39300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>41800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>16300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>15000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>22700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>36400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>20400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>20800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,308 +1949,322 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-6700</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-10200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F21" s="3">
         <v>6600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>12100</v>
       </c>
-      <c r="F21" s="3">
-        <v>7800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>22900</v>
-      </c>
       <c r="H21" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>23600</v>
+      </c>
+      <c r="J21" s="3">
         <v>2800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>6200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>21800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-118500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>16300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-26300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>10600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>19100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>35400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>37000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>48500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>44600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>35900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>35300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>47500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>51100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>37100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>50400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>58400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>59300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>15500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>18600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>30900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>26000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>40100</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F22" s="3">
         <v>7100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>7600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>9000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>10600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>11200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>13600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>12000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>13000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>11300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>10500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>8700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>8100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>7900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>8300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>8600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>8800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>9100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>9500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>10400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>11700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>12600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>13600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>13500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>13800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>14800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>15300</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>14100</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF22" s="3">
         <v>14100</v>
@@ -2192,8 +2272,8 @@
       <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>8</v>
+      <c r="AH22" s="3">
+        <v>14100</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>8</v>
@@ -2204,222 +2284,240 @@
       <c r="AK22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-62500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-116300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-24500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-20700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>11700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-57000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-31300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-50300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-37200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-10000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-148600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-12500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-55200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-9900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>5800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>7600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>18900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>14500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>4900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>14300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>17100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>3900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>17300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>25000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>26600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>3000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>10200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>24500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>10600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-2800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-33000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-12400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>4800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>3200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>3500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>4800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>4100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>5900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>7900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>4700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>9100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>3900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2623,240 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-114600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-24900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-19900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>11700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-57900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-28300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-47600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-35100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-9100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-115600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-10000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-42800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>4300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>5700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>14100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>11400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>3400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>10800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>12200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>3000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>13200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>19100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>18800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>2400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>1200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>5500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>15400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>6600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-114600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-24900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-19900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>11700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-57900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-28300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-47600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-35100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-9100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-115600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-10000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-42800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>4300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>5700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>14100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>11400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>3400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>10800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>12200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>3000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>13200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>19100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>18800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>2400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>1200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>5500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>15400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>6600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2962,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2908,11 +3030,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2926,24 +3048,24 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>600</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>21400</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2953,8 +3075,14 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3188,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3301,240 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>6500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>6700</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>13300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>12500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>11900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>10200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-114600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-24900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-19900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>11700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-57900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-28300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-47600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-35100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-9100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-115600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-10000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-42800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-7500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>4300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>5700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>14100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>11400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>10800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>12200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>3000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>13200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>19100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>19400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>2400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>22600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>5500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>15400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>6600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3640,245 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-114600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-24900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-19900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>11700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-57900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-28300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-47600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-35100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-9100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-115600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-10000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-42800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-7500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>4300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>5700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>14100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>11400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>10800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>12200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>3000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>13200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>19100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>19400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>2400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>22600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>5500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>15400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>6600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3916,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,101 +3957,103 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>54100</v>
+      </c>
+      <c r="F41" s="3">
         <v>40000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>18500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>16100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>32900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>48300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>51400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>56100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>57700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>54400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>75900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>102300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>120500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>180400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>147900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>181300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>99400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>64900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>52400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>57800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>68900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>79900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>77700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>88600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>103300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>41700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>52700</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3892,8 +4066,14 @@
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3904,14 +4084,14 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>5400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3970,17 +4150,17 @@
         <v>0</v>
       </c>
       <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>15000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>19900</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3990,110 +4170,116 @@
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F43" s="3">
         <v>5300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>5500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>8300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>9900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>13100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>6800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>13900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>15400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>13700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>14600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>14200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>24100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>23100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>7900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>12100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>6000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>14300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>21600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>17000</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4106,101 +4292,107 @@
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F44" s="3">
         <v>29200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>28300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>30700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>29500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>28800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>29200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>28700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>26800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>25500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>26700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>26300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>26300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>25200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>24500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>24700</v>
-      </c>
-      <c r="S44" s="3">
-        <v>23000</v>
-      </c>
-      <c r="T44" s="3">
-        <v>22800</v>
       </c>
       <c r="U44" s="3">
         <v>23000</v>
       </c>
       <c r="V44" s="3">
-        <v>22400</v>
+        <v>22800</v>
       </c>
       <c r="W44" s="3">
-        <v>22400</v>
+        <v>23000</v>
       </c>
       <c r="X44" s="3">
         <v>22400</v>
       </c>
       <c r="Y44" s="3">
+        <v>22400</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AA44" s="3">
         <v>21300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>20300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>19200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>17400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>15700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>15700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>15400</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
@@ -4213,101 +4405,107 @@
       <c r="AK44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>75800</v>
+      </c>
+      <c r="F45" s="3">
         <v>80700</v>
       </c>
-      <c r="E45" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H45" s="3">
         <v>20200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>39100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>92400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>58800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>91300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>19700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>10000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>10600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>11000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>7800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>10200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>12300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>12300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>16500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>19500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>10600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>9400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>8000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>44600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>50100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>51100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>46700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>44700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>43300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>51000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4320,101 +4518,107 @@
       <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>133400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>163600</v>
+      </c>
+      <c r="F46" s="3">
         <v>160700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>61300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>84900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>98400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>150300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>138600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>181100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>117100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>102000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>98300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>95400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>120000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>138300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>158400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>222400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>197100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>236000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>155600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>112600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>98300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>112200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>157800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>158200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>160100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>173700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>197900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>122400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>136200</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
@@ -4427,56 +4631,62 @@
       <c r="AK46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>300</v>
       </c>
       <c r="F47" s="3">
         <v>300</v>
       </c>
       <c r="G47" s="3">
+        <v>300</v>
+      </c>
+      <c r="H47" s="3">
+        <v>300</v>
+      </c>
+      <c r="I47" s="3">
         <v>11400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>23000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>20300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>18200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>15300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>13400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>15200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>16600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>19900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>19000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4495,33 +4705,33 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA47" s="3">
         <v>3900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>4500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>5000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>4100</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG47" s="3">
         <v>2500</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4534,101 +4744,107 @@
       <c r="AK47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>43900</v>
+      </c>
+      <c r="F48" s="3">
         <v>210200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>433600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>505200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>537600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>543400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>707700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>721100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>879600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>957400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>908300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1138700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1144100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1246400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1245000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1262100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1286200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1308700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1335700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1365200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1383600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1407300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1273600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1286000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1237600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1247800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1250800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1239500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1182800</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
@@ -4641,8 +4857,14 @@
       <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4674,68 +4896,68 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>3800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>6000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>6300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>6500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>6800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>7100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>7400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>7700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>8000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>8400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>8800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>9200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>9500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>10000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>10400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>10900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>11300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>11400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>11500</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4748,8 +4970,14 @@
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +5083,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,101 +5196,107 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7400</v>
+        <v>1300</v>
       </c>
       <c r="E52" s="3">
-        <v>95600</v>
+        <v>2200</v>
       </c>
       <c r="F52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G52" s="3">
+        <v>89200</v>
+      </c>
+      <c r="H52" s="3">
         <v>59900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>44700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>43400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>15100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>23700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>24200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>76400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>89900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>63400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>63200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>24300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>46400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>33500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>28900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>9100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>21100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>13300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>7100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>7300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>12100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>7500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>12300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>16200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>9600</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5069,8 +5309,14 @@
       <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,101 +5422,107 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>178600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F54" s="3">
         <v>383600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>596900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>664400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>706300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>775600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>898500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>962000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1055400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1159500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1115600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1320200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1353400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1434500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1456600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1525000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1519600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1554800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1501900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1495300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1511700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1542000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1451900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1466000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1425300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1444000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1472400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1389600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1342600</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
@@ -5283,8 +5535,14 @@
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5580,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,101 +5621,103 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>56000</v>
+      </c>
+      <c r="F57" s="3">
         <v>60900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>72100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>64400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>57300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>54500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>59000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>51900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>48500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>51300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>59400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>66800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>76700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>62900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>61500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>52800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>70000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>47600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>53200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>39900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>49200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>47800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>49900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>33600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>40500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>40400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>54300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>44700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>41900</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>8</v>
       </c>
@@ -5468,101 +5730,107 @@
       <c r="AK57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>86400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>100100</v>
+      </c>
+      <c r="F58" s="3">
         <v>144700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>52100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>75000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>96700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>160000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>167100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>128700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>150600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>94200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>97200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>112800</v>
-      </c>
-      <c r="O58" s="3">
-        <v>111700</v>
-      </c>
-      <c r="P58" s="3">
-        <v>111100</v>
       </c>
       <c r="Q58" s="3">
         <v>111700</v>
       </c>
       <c r="R58" s="3">
+        <v>111100</v>
+      </c>
+      <c r="S58" s="3">
+        <v>111700</v>
+      </c>
+      <c r="T58" s="3">
         <v>107700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>104000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>99700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>189300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>176900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>168200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>166100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>165900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>163600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>147100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>149800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>155200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>149900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>144500</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5575,101 +5843,107 @@
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F59" s="3">
         <v>5900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>4000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>6500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>57900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>60700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>61000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>76400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>85000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>115400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>87400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>140600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>110800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>91200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>83200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>82100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>40900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>48600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>39000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>40900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>41900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>52300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>33900</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5682,101 +5956,107 @@
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>174600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>202000</v>
+      </c>
+      <c r="F60" s="3">
         <v>253100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>174500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>187500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>196800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>253900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>267900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>222100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>242100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>186300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>214500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>240300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>249400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>250400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>258200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>276000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>261400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>287900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>353300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>308000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>300600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>295900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>256700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>245900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>226700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>231200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>251400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>246900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>220400</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
@@ -5789,101 +6069,107 @@
       <c r="AK60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>38500</v>
+      </c>
+      <c r="F61" s="3">
         <v>90300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>266700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>294200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>306300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>323200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>372800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>450900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>472100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>607300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>502500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>523200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>521500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>547400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>539700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>585800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>600100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>624100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>542500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>586900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>619800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>641000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>677400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>717500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>696900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>727800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>760200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>828500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>784500</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -5896,101 +6182,107 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>28700</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>31600</v>
+        <v>25200</v>
       </c>
       <c r="F62" s="3">
+        <v>28200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>31100</v>
+      </c>
+      <c r="H62" s="3">
         <v>31400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>31800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>32600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>32700</v>
       </c>
       <c r="J62" s="3">
         <v>32600</v>
       </c>
       <c r="K62" s="3">
+        <v>32700</v>
+      </c>
+      <c r="L62" s="3">
+        <v>32600</v>
+      </c>
+      <c r="M62" s="3">
         <v>31400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>31000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>90400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>133600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>150000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>162200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>170700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>168600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>167300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>158500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>148300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>154900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>150000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>166900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>91900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>89900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>92500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>89700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>86400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>81600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>89100</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6003,8 +6295,14 @@
       <c r="AK62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6408,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6521,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,101 +6634,107 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>219900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>277400</v>
+      </c>
+      <c r="F66" s="3">
         <v>387600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>486600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>529500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>551600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>633000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>698400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>734100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>780100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>859700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>807400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>897100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>920800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>960000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>968600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1030300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1028700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1070500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1044100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1049800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1070400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1103800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1026000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1053200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1016000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1048800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1097900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1157000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1093900</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
@@ -6431,8 +6747,14 @@
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6792,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6901,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +7014,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +7127,14 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,101 +7240,107 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-314500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-335300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-276700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-162100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-137200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-117300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-129000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-71100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-42800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>39900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>49000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>164600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>174600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>217400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>231700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>239200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>234900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>229200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>215100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>203700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>200300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>198400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>187400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>175100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>172100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>158900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>139800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>119900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>133400</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7005,8 +7353,14 @@
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7466,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7579,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,101 +7692,107 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-4000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>110200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>134900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>154700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>142600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>200000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>227900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>275200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>299800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>308200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>423000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>432500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>474500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>488000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>494700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>490800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>484300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>457900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>445500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>441400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>438200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>425900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>412700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>409300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>395200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>374500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>232600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>248700</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
@@ -7433,8 +7805,14 @@
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7918,245 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-114600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-24900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-19900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>11700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-57900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-28300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-47600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-35100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-9100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-115600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-10000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-42800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-7500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>4300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>5700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>14100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>11400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>10800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>12200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>3000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>13200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>19100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>19400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>2400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>22600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>5500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>15400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>6600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,70 +8194,72 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F83" s="3">
         <v>13300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>13300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>15300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>17300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>14400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>19400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>19800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>20500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>20700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>19600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>20100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>20700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>21000</v>
       </c>
       <c r="Q83" s="3">
         <v>20700</v>
       </c>
       <c r="R83" s="3">
-        <v>20900</v>
+        <v>21000</v>
       </c>
       <c r="S83" s="3">
         <v>20700</v>
       </c>
       <c r="T83" s="3">
+        <v>20900</v>
+      </c>
+      <c r="U83" s="3">
+        <v>20700</v>
+      </c>
+      <c r="V83" s="3">
         <v>20500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>20600</v>
-      </c>
-      <c r="V83" s="3">
-        <v>20600</v>
-      </c>
-      <c r="W83" s="3">
-        <v>20500</v>
       </c>
       <c r="X83" s="3">
         <v>20600</v>
@@ -7870,43 +8268,49 @@
         <v>20500</v>
       </c>
       <c r="Z83" s="3">
+        <v>20600</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="AB83" s="3">
         <v>19800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>19300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>18500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>17400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>16000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>15700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>15900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>15800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>15600</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK83" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM83" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8416,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8529,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8642,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8755,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8868,127 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-11600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>14600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>11200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>16200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-7800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-10300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>5200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>52600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>79300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>71100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>38400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>27000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>38200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>37600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>44300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>25600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>44100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>55800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>22000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>13100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>28100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>36000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>22200</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK89" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM89" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +9026,123 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-6300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-6900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-5000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-7100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-7800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-16700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-10400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-3100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-6400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-5500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-12200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-2800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-19500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-81500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK91" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM91" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9248,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9361,127 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>62100</v>
+      </c>
+      <c r="F94" s="3">
         <v>115800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>35900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>18400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>47900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>46600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>33300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>47200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>78400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-16600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>41700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-10400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-16400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-5400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-9900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-11900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>1800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-37400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-84200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK94" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM94" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9519,10 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9085,11 +9553,11 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -9160,8 +9628,14 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9741,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9854,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,115 +9967,127 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-79900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-51200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-31900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-61800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-55600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-38500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-45100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-80700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>21000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-38300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-14700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-28600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>4000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-45100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-14700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-23100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>4600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-35000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-25500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-20400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-36700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-39800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>35400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-38300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-38700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>43200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>51300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-32700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>4600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>14300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-22900</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK100" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM100" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9620,11 +10118,11 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -9695,111 +10193,123 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F102" s="3">
         <v>24400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-16900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-15400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-21500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-26400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-59900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>32500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-33700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>82100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>34500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>12500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-5400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>2200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-14900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>61600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-26300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>22500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>33900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
